--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486976_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486976_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3837</v>
+        <v>5.0939</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2529</v>
+        <v>3.3188</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1308</v>
+        <v>1.7751</v>
       </c>
       <c r="G2" t="n">
         <v>3.1171</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4987</v>
+        <v>1.2089</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4725</v>
+        <v>0.5384</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0262</v>
+        <v>0.6705</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8021</v>
+        <v>4.247</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6396</v>
+        <v>5.1437</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8375</v>
+        <v>-0.8968</v>
       </c>
       <c r="G3" t="n">
         <v>0.1482</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5451</v>
+        <v>0.9899</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3093</v>
+        <v>0.8134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2358</v>
+        <v>0.1765</v>
       </c>
       <c r="V3" t="n">
         <v>1.8768</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4105</v>
+        <v>2.7133</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6554</v>
+        <v>2.2571</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.245</v>
+        <v>0.4562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1638</v>
+        <v>1.742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1136</v>
+        <v>2.5209</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0502</v>
+        <v>-0.779</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8966</v>
+        <v>2.6671</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7782</v>
+        <v>3.3778</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1184</v>
+        <v>-0.7108</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7328</v>
+        <v>-0.9251</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6646</v>
+        <v>-0.8569</v>
       </c>
       <c r="O4" t="n">
         <v>-0.0682</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1502</v>
+        <v>1.0596</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0648</v>
+        <v>0.4648</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0854</v>
+        <v>0.5949</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4805</v>
+        <v>0.9384</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2402</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1697</v>
+        <v>1.8414</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7728</v>
+        <v>2.0864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3969</v>
+        <v>-0.245</v>
       </c>
       <c r="G5" t="n">
-        <v>1.742</v>
+        <v>0.1638</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5209</v>
+        <v>0.1136</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.779</v>
+        <v>0.0502</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6671</v>
+        <v>1.8966</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3778</v>
+        <v>1.7782</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7108</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9251</v>
+        <v>-1.7328</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8569</v>
+        <v>-1.6646</v>
       </c>
       <c r="O5" t="n">
         <v>-0.0682</v>
       </c>
       <c r="P5" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5161</v>
+        <v>0.5812</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0195</v>
+        <v>0.4958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5356</v>
+        <v>0.0854</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9384</v>
+        <v>0.4805</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>0.7207</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2402</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2355</v>
+        <v>0.9429</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.37</v>
+        <v>0.2189</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6055</v>
+        <v>0.7241</v>
       </c>
       <c r="G6" t="n">
         <v>3.6046</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4943</v>
+        <v>0.2132</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6587</v>
+        <v>-0.0698</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1644</v>
+        <v>0.283</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0399</v>
+        <v>0.3036</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2899</v>
+        <v>-0.9761</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.2797</v>
       </c>
       <c r="G7" t="n">
         <v>-1.497</v>
@@ -1000,13 +1000,13 @@
         <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0465</v>
+        <v>1.3899</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5075</v>
+        <v>0.8213</v>
       </c>
       <c r="U7" t="n">
-        <v>0.539</v>
+        <v>0.5687</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6464</v>
+        <v>-0.6651</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0109</v>
+        <v>-0.4529</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6355</v>
+        <v>-0.2121</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0568</v>
+        <v>-1.6589</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1936</v>
+        <v>0.483</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1368</v>
+        <v>-2.1419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8454</v>
+        <v>-0.1468</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6351</v>
+        <v>1.0901</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7897</v>
+        <v>-1.2368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7887</v>
+        <v>-1.5121</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4415</v>
+        <v>-0.6071</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3472</v>
+        <v>-0.905</v>
       </c>
       <c r="P8" t="n">
         <v>-0.2053</v>
@@ -1078,28 +1078,28 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6808</v>
+        <v>0.9589</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1704</v>
+        <v>0.4803</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5104</v>
+        <v>0.4786</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8948</v>
+        <v>-0.6695</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6234</v>
+        <v>0.055</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2714</v>
+        <v>-0.7245</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6589</v>
+        <v>0.0568</v>
       </c>
       <c r="H9" t="n">
-        <v>0.483</v>
+        <v>1.1936</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1419</v>
+        <v>-1.1368</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1468</v>
+        <v>0.8454</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0901</v>
+        <v>1.6351</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2368</v>
+        <v>-0.7897</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5121</v>
+        <v>-0.7887</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6071</v>
+        <v>-0.4415</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.905</v>
+        <v>-0.3472</v>
       </c>
       <c r="P9" t="n">
         <v>-0.2053</v>
@@ -1156,22 +1156,22 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7291</v>
+        <v>0.6577</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3098</v>
+        <v>0.2362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4193</v>
+        <v>0.4215</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9346</v>
+        <v>-1.6612</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1514</v>
+        <v>0.2173</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.086</v>
+        <v>-1.8785</v>
       </c>
       <c r="G10" t="n">
         <v>0.4618</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.191</v>
+        <v>0.0823</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1704</v>
+        <v>0.2362</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3614</v>
+        <v>-0.1539</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0981</v>
+        <v>-1.898</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8438</v>
+        <v>-0.6733</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2543</v>
+        <v>-1.2246</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7765</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3832</v>
+        <v>-0.1831</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2635</v>
+        <v>-0.093</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9384</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4888</v>
+        <v>-2.6907</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4224</v>
+        <v>0.3757</v>
       </c>
       <c r="F12" t="n">
         <v>-3.0664</v>
@@ -1390,10 +1390,10 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6083</v>
+        <v>0.1898</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5192</v>
+        <v>0.2788</v>
       </c>
       <c r="U12" t="n">
         <v>-0.0891</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.898900000000001</v>
+        <v>7.557599999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>10.9117</v>
+        <v>11.5706</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.012899999999999</v>
+        <v>-4.0128</v>
       </c>
       <c r="G13" t="n">
         <v>4.2761</v>
@@ -1468,13 +1468,13 @@
         <v>10.2672</v>
       </c>
       <c r="S13" t="n">
-        <v>6.489700000000001</v>
+        <v>7.148300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5438</v>
+        <v>4.2024</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9459</v>
+        <v>2.945999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.2403000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6357</v>
+        <v>5.8815</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1614</v>
+        <v>6.4752</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5937</v>
       </c>
       <c r="G14" t="n">
         <v>4.793</v>
@@ -1546,13 +1546,13 @@
         <v>2.8748</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.533</v>
+        <v>-1.2873</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0812</v>
+        <v>-0.7674</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4518</v>
+        <v>-0.5199</v>
       </c>
       <c r="V14" t="n">
         <v>0.9384</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.959</v>
+        <v>0.755</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4148</v>
+        <v>3.101</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4558</v>
+        <v>-2.346</v>
       </c>
       <c r="G15" t="n">
         <v>0.8517</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3568</v>
+        <v>-0.5608</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2167</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5736</v>
+        <v>-0.4638</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1786</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5773</v>
+        <v>0.4413</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9044</v>
+        <v>1.5906</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3271</v>
+        <v>-1.1492</v>
       </c>
       <c r="G16" t="n">
         <v>0.0171</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2612</v>
+        <v>-0.3972</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0464</v>
+        <v>-0.2674</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3076</v>
+        <v>-0.1297</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6289</v>
+        <v>-0.2662</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3244</v>
+        <v>1.429</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9533</v>
+        <v>-1.6953</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3278</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0794</v>
+        <v>-0.7168</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3489</v>
+        <v>-0.2443</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7305</v>
+        <v>-0.4725</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.998</v>
+        <v>-0.7452</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0476</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0496</v>
+        <v>0.1978</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1514</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4359</v>
+        <v>-0.1831</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3952</v>
+        <v>-0.2906</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0407</v>
+        <v>0.1075</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1659</v>
+        <v>-1.9968</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9234</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2425</v>
+        <v>-1.0734</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6824</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8675</v>
+        <v>-0.6984</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3952</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4722</v>
+        <v>-0.3031</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0311</v>
+        <v>-2.0485</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8244</v>
+        <v>-1.2546</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2067</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3621</v>
+        <v>-3.7216</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8069</v>
+        <v>-2.8902</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4448</v>
+        <v>-0.8315</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6634</v>
+        <v>-1.5497</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.639</v>
+        <v>-1.365</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3024</v>
+        <v>-0.1847</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0255</v>
+        <v>-2.172</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1679</v>
+        <v>-1.5252</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8575</v>
+        <v>-0.6468</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4107</v>
+        <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0531</v>
+        <v>-0.9696</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4611</v>
+        <v>-0.4729</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.592</v>
+        <v>-0.4967</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2706</v>
+        <v>-2.9719</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0914</v>
+        <v>-0.8244</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1792</v>
+        <v>-2.1475</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7216</v>
+        <v>-1.3621</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8902</v>
+        <v>-1.8069</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8315</v>
+        <v>0.4448</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5497</v>
+        <v>0.6634</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.365</v>
+        <v>-0.639</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1847</v>
+        <v>1.3024</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.172</v>
+        <v>-2.0255</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5252</v>
+        <v>-1.1679</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6468</v>
+        <v>-0.8575</v>
       </c>
       <c r="P22" t="n">
-        <v>2.0534</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4641</v>
+        <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1918</v>
+        <v>-0.9938</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3097</v>
+        <v>-0.4611</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.882</v>
+        <v>-0.5327</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8956</v>
+        <v>-5.1701</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1158</v>
+        <v>-3.848</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7798</v>
+        <v>-1.3221</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1189</v>
@@ -2248,13 +2248,13 @@
         <v>2.2588</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6997</v>
+        <v>0.4252</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9141</v>
+        <v>0.1819</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7857</v>
+        <v>0.2434</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2177</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8989</v>
+        <v>-6.201700000000001</v>
       </c>
       <c r="E24" t="n">
         <v>4.0128</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.9117</v>
+        <v>-10.2145</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.276</v>
+        <v>-4.275999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-4.7511</v>
@@ -2326,13 +2326,13 @@
         <v>14.374</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.489700000000001</v>
+        <v>-5.7925</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.945800000000001</v>
+        <v>-2.9458</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5436</v>
+        <v>-2.8464</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2402000000000001</v>
